--- a/游戏设计王/老虎机数学专题-巨型图案.xlsx
+++ b/游戏设计王/老虎机数学专题-巨型图案.xlsx
@@ -457,12 +457,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0000%"/>
+    <numFmt numFmtId="177" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -1155,7 +1156,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1242,6 +1243,13 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4732,7 +4740,7 @@
       <c r="C27" s="4">
         <v>0</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="44">
         <f>((B$6*C$6*D$6*(H$26-E$6)*(I$26-F$6))*B$17+(B$6*C$6*D$6*E$6*(I$26-F$6))*C$17+(B$6*C$6*D$6*E$6*F$6)*D$17+(B$7*C$7*D$7*(H$26-E$7)*(I$26-F$7))*B$18+(B$7*C$7*D$7*E$7*(I$26-F$7))*C$18+(B$7*C$7*D$7*E$7*F$7)*D$18+(B$8*C$8*D$8*(H$26-E$8)*(I$26-F$8))*B$19+(B$8*C$8*D$8*E$8*(I$26-F$8))*C$19+(B$8*C$8*D$8*E$8*F$8)*D$19+(B$9*C$9*D$9*(H$26-E$9)*(I$26-F$9))*B$20+(B$9*C$9*D$9*E$9*(I$26-F$9))*C$20+(B$9*C$9*D$9*E$9*F$9)*D$20+(B$10*C$10*D$10*(H$26-E$10)*(I$26-F$10))*B$21+(B$10*C$10*D$10*E$10*(I$26-F$10))*C$21+(B$10*C$10*D$10*E$10*F$10)*D$21)/PRODUCT($E$26:$I$26)</f>
         <v>0.20512</v>
       </c>
@@ -4765,7 +4773,7 @@
       <c r="C28" s="4">
         <v>0</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="44">
         <f>((B$6*F$26*D$6*(H$26-E$6)*(I$26-F$6))*B$17+(B$6*F$26*D$6*E$6*(I$26-F$6))*C$17+(B$6*F$26*D$6*E$6*F$6)*D$17+(B$7*F$26*D$7*(H$26-E$7)*(I$26-F$7))*B$18+(B$7*F$26*D$7*E$7*(I$26-F$7))*C$18+(B$7*F$26*D$7*E$7*F$7)*D$18+(B$8*F$26*D$8*(H$26-E$8)*(I$26-F$8))*B$19+(B$8*F$26*D$8*E$8*(I$26-F$8))*C$19+(B$8*F$26*D$8*E$8*F$8)*D$19+(B$9*F$26*D$9*(H$26-E$9)*(I$26-F$9))*B$20+(B$9*F$26*D$9*E$9*(I$26-F$9))*C$20+(B$9*F$26*D$9*E$9*F$9)*D$20+(B$10*F$26*D$10*(H$26-E$10)*(I$26-F$10))*B$21+(B$10*F$26*D$10*E$10*(I$26-F$10))*C$21+(B$10*F$26*D$10*E$10*F$10)*D$21)/PRODUCT($E$26:$I$26)</f>
         <v>1.0256</v>
       </c>
@@ -4798,7 +4806,7 @@
       <c r="C29" s="4">
         <v>0</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="44">
         <f>((B$6*C$6*G$26*(H$26-E$6)*(I$26-F$6))*B$17+(B$6*C$6*G$26*E$6*(I$26-F$6))*C$17+(B$6*C$6*G$26*E$6*F$6)*D$17+(B$7*C$7*G$26*(H$26-E$7)*(I$26-F$7))*B$18+(B$7*C$7*G$26*E$7*(I$26-F$7))*C$18+(B$7*C$7*G$26*E$7*F$7)*D$18+(B$8*C$8*G$26*(H$26-E$8)*(I$26-F$8))*B$19+(B$8*C$8*G$26*E$8*(I$26-F$8))*C$19+(B$8*C$8*G$26*E$8*F$8)*D$19+(B$9*C$9*G$26*(H$26-E$9)*(I$26-F$9))*B$20+(B$9*C$9*G$26*E$9*(I$26-F$9))*C$20+(B$9*C$9*G$26*E$9*F$9)*D$20+(B$10*C$10*G$26*(H$26-E$10)*(I$26-F$10))*B$21+(B$10*C$10*G$26*E$10*(I$26-F$10))*C$21+(B$10*C$10*G$26*E$10*F$10)*D$21)/PRODUCT($E$26:$I$26)</f>
         <v>1.0256</v>
       </c>
@@ -4831,7 +4839,7 @@
       <c r="C30" s="4">
         <v>0</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="44">
         <f>((B$6*F$26*G$26*(H$26-E$6)*(I$26-F$6))*B$17+(B$6*F$26*G$26*E$6*(I$26-F$6))*C$17+(B$6*F$26*G$26*E$6*F$6)*D$17+(B$7*F$26*G$26*(H$26-E$7)*(I$26-F$7))*B$18+(B$7*F$26*G$26*E$7*(I$26-F$7))*C$18+(B$7*F$26*G$26*E$7*F$7)*D$18+(B$8*F$26*G$26*(H$26-E$8)*(I$26-F$8))*B$19+(B$8*F$26*G$26*E$8*(I$26-F$8))*C$19+(B$8*F$26*G$26*E$8*F$8)*D$19+(B$9*F$26*G$26*(H$26-E$9)*(I$26-F$9))*B$20+(B$9*F$26*G$26*E$9*(I$26-F$9))*C$20+(B$9*F$26*G$26*E$9*F$9)*D$20+(B$10*F$26*G$26*(H$26-E$10)*(I$26-F$10))*B$21+(B$10*F$26*G$26*E$10*(I$26-F$10))*C$21+(B$10*F$26*G$26*E$10*F$10)*D$21)/PRODUCT($E$26:$I$26)</f>
         <v>5.128</v>
       </c>
@@ -4864,7 +4872,7 @@
       <c r="C31" s="4">
         <v>1</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="44">
         <f>((B$6*C$6*D$6*(H$26-H$26)*(I$26-F$6))*B$17+(B$6*C$6*D$6*H$26*(I$26-F$6))*C$17+(B$6*C$6*D$6*H$26*F$6)*D$17+(B$7*C$7*D$7*(H$26-H$26)*(I$26-F$7))*B$18+(B$7*C$7*D$7*H$26*(I$26-F$7))*C$18+(B$7*C$7*D$7*H$26*F$7)*D$18+(B$8*C$8*D$8*(H$26-H$26)*(I$26-F$8))*B$19+(B$8*C$8*D$8*H$26*(I$26-F$8))*C$19+(B$8*C$8*D$8*H$26*F$8)*D$19+(B$9*C$9*D$9*(H$26-H$26)*(I$26-F$9))*B$20+(B$9*C$9*D$9*H$26*(I$26-F$9))*C$20+(B$9*C$9*D$9*H$26*F$9)*D$20+(B$10*C$10*D$10*(H$26-H$26)*(I$26-F$10))*B$21+(B$10*C$10*D$10*H$26*(I$26-F$10))*C$21+(B$10*C$10*D$10*H$26*F$10)*D$21)/PRODUCT($E$26:$I$26)</f>
         <v>0.5904</v>
       </c>
@@ -4897,7 +4905,7 @@
       <c r="C32" s="4">
         <v>1</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="44">
         <f>((B$6*F$26*D$6*(H$26-H$26)*(I$26-F$6))*B$17+(B$6*F$26*D$6*H$26*(I$26-F$6))*C$17+(B$6*F$26*D$6*H$26*F$6)*D$17+(B$7*F$26*D$7*(H$26-H$26)*(I$26-F$7))*B$18+(B$7*F$26*D$7*H$26*(I$26-F$7))*C$18+(B$7*F$26*D$7*H$26*F$7)*D$18+(B$8*F$26*D$8*(H$26-H$26)*(I$26-F$8))*B$19+(B$8*F$26*D$8*H$26*(I$26-F$8))*C$19+(B$8*F$26*D$8*H$26*F$8)*D$19+(B$9*F$26*D$9*(H$26-H$26)*(I$26-F$9))*B$20+(B$9*F$26*D$9*H$26*(I$26-F$9))*C$20+(B$9*F$26*D$9*H$26*F$9)*D$20+(B$10*F$26*D$10*(H$26-H$26)*(I$26-F$10))*B$21+(B$10*F$26*D$10*H$26*(I$26-F$10))*C$21+(B$10*F$26*D$10*H$26*F$10)*D$21)/PRODUCT($E$26:$I$26)</f>
         <v>2.952</v>
       </c>
@@ -4930,7 +4938,7 @@
       <c r="C33" s="4">
         <v>1</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="44">
         <f>((B$6*C$6*G$26*(H$26-H$26)*(I$26-F$6))*B$17+(B$6*C$6*G$26*H$26*(I$26-F$6))*C$17+(B$6*C$6*G$26*H$26*F$6)*D$17+(B$7*C$7*G$26*(H$26-H$26)*(I$26-F$7))*B$18+(B$7*C$7*G$26*H$26*(I$26-F$7))*C$18+(B$7*C$7*G$26*H$26*F$7)*D$18+(B$8*C$8*G$26*(H$26-H$26)*(I$26-F$8))*B$19+(B$8*C$8*G$26*H$26*(I$26-F$8))*C$19+(B$8*C$8*G$26*H$26*F$8)*D$19+(B$9*C$9*G$26*(H$26-H$26)*(I$26-F$9))*B$20+(B$9*C$9*G$26*H$26*(I$26-F$9))*C$20+(B$9*C$9*G$26*H$26*F$9)*D$20+(B$10*C$10*G$26*(H$26-H$26)*(I$26-F$10))*B$21+(B$10*C$10*G$26*H$26*(I$26-F$10))*C$21+(B$10*C$10*G$26*H$26*F$10)*D$21)/PRODUCT($E$26:$I$26)</f>
         <v>2.952</v>
       </c>
@@ -4963,7 +4971,7 @@
       <c r="C34" s="4">
         <v>1</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="44">
         <f>((B$6*F$26*G$26*(H$26-H$26)*(I$26-F$6))*B$17+(B$6*F$26*G$26*H$26*(I$26-F$6))*C$17+(B$6*F$26*G$26*H$26*F$6)*D$17+(B$7*F$26*G$26*(H$26-H$26)*(I$26-F$7))*B$18+(B$7*F$26*G$26*H$26*(I$26-F$7))*C$18+(B$7*F$26*G$26*H$26*F$7)*D$18+(B$8*F$26*G$26*(H$26-H$26)*(I$26-F$8))*B$19+(B$8*F$26*G$26*H$26*(I$26-F$8))*C$19+(B$8*F$26*G$26*H$26*F$8)*D$19+(B$9*F$26*G$26*(H$26-H$26)*(I$26-F$9))*B$20+(B$9*F$26*G$26*H$26*(I$26-F$9))*C$20+(B$9*F$26*G$26*H$26*F$9)*D$20+(B$10*F$26*G$26*(H$26-H$26)*(I$26-F$10))*B$21+(B$10*F$26*G$26*H$26*(I$26-F$10))*C$21+(B$10*F$26*G$26*H$26*F$10)*D$21)/PRODUCT($E$26:$I$26)</f>
         <v>14.76</v>
       </c>
@@ -5546,15 +5554,15 @@
       <c r="E52" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F52" s="9">
+      <c r="F52" s="44">
         <f>D27</f>
         <v>0.20512</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52" s="44">
         <f>D27</f>
         <v>0.20512</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H52" s="44">
         <f>D27</f>
         <v>0.20512</v>
       </c>
@@ -5581,15 +5589,15 @@
       <c r="E53" s="43">
         <v>100</v>
       </c>
-      <c r="F53" s="9">
+      <c r="F53" s="44">
         <f>D27</f>
         <v>0.20512</v>
       </c>
-      <c r="G53" s="9">
+      <c r="G53" s="44">
         <f>D27</f>
         <v>0.20512</v>
       </c>
-      <c r="H53" s="9">
+      <c r="H53" s="44">
         <f>D28</f>
         <v>1.0256</v>
       </c>
@@ -5616,15 +5624,15 @@
       <c r="E54" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F54" s="9">
+      <c r="F54" s="44">
         <f>D27</f>
         <v>0.20512</v>
       </c>
-      <c r="G54" s="9">
+      <c r="G54" s="44">
         <f>D29</f>
         <v>1.0256</v>
       </c>
-      <c r="H54" s="9">
+      <c r="H54" s="44">
         <f>D31</f>
         <v>0.5904</v>
       </c>
@@ -5651,15 +5659,15 @@
       <c r="E55" s="43">
         <v>110</v>
       </c>
-      <c r="F55" s="9">
+      <c r="F55" s="44">
         <f>D34</f>
         <v>14.76</v>
       </c>
-      <c r="G55" s="9">
+      <c r="G55" s="44">
         <f>D32</f>
         <v>2.952</v>
       </c>
-      <c r="H55" s="9">
+      <c r="H55" s="44">
         <f>D30</f>
         <v>5.128</v>
       </c>
@@ -5686,15 +5694,15 @@
       <c r="E56" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F56" s="9">
+      <c r="F56" s="44">
         <f>D34</f>
         <v>14.76</v>
       </c>
-      <c r="G56" s="9">
+      <c r="G56" s="44">
         <f>D34</f>
         <v>14.76</v>
       </c>
-      <c r="H56" s="9">
+      <c r="H56" s="44">
         <f>D33</f>
         <v>2.952</v>
       </c>
@@ -5721,15 +5729,15 @@
       <c r="E57" s="43">
         <v>111</v>
       </c>
-      <c r="F57" s="9">
+      <c r="F57" s="44">
         <f>D34</f>
         <v>14.76</v>
       </c>
-      <c r="G57" s="9">
+      <c r="G57" s="44">
         <f>D34</f>
         <v>14.76</v>
       </c>
-      <c r="H57" s="9">
+      <c r="H57" s="44">
         <f>D34</f>
         <v>14.76</v>
       </c>
@@ -5776,7 +5784,7 @@
       <c r="A59" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B59" s="11">
+      <c r="B59" s="46">
         <f>SUM(B52:B57)</f>
         <v>1</v>
       </c>
@@ -5809,7 +5817,7 @@
       <c r="A60" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60" s="44">
         <f>SUMPRODUCT($B$52:$B$57,F52:F57)</f>
         <v>8.938048</v>
       </c>
@@ -5842,7 +5850,7 @@
       <c r="A61" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B61" s="9">
+      <c r="B61" s="44">
         <f>SUMPRODUCT($B$52:$B$57,G52:G57)</f>
         <v>6.69952</v>
       </c>
@@ -5875,7 +5883,7 @@
       <c r="A62" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B62" s="9">
+      <c r="B62" s="44">
         <f>SUMPRODUCT($B$52:$B$57,H52:H57)</f>
         <v>4.830912</v>
       </c>
@@ -5908,7 +5916,7 @@
       <c r="A63" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="12">
+      <c r="B63" s="47">
         <f>AVERAGE(B60:B62)</f>
         <v>6.82282666666667</v>
       </c>
@@ -6387,7 +6395,7 @@
       <c r="F77" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G77" s="12">
+      <c r="G77" s="47">
         <f>SUM(G71:G75)/PRODUCT(B$4:D$4)</f>
         <v>2.952</v>
       </c>
@@ -6501,7 +6509,7 @@
       <c r="A81" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B81" s="13">
+      <c r="B81" s="48">
         <f>B63</f>
         <v>6.82282666666667</v>
       </c>
@@ -6534,7 +6542,7 @@
       <c r="A82" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B82" s="9">
+      <c r="B82" s="44">
         <f>G77</f>
         <v>2.952</v>
       </c>
